--- a/scripts/out_syscohada/journaux_ci.xlsx
+++ b/scripts/out_syscohada/journaux_ci.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="132">
   <si>
     <t>YAHRIA BUSINESS OS — ÉTATS FINANCIERS SYSCOHADA (SYSTÈME NORMAL)</t>
   </si>
@@ -118,6 +118,123 @@
     <t>Journal PAIE — Journal de paie</t>
   </si>
   <si>
+    <t>31/07/2026</t>
+  </si>
+  <si>
+    <t>PAIE-2026-07-CMU0C857/P1</t>
+  </si>
+  <si>
+    <t>6613</t>
+  </si>
+  <si>
+    <t>Salaires des chefs d’exploitation et de main-d’œuvre</t>
+  </si>
+  <si>
+    <t>6641</t>
+  </si>
+  <si>
+    <t>Cotisations sociales patronales</t>
+  </si>
+  <si>
+    <t>4311</t>
+  </si>
+  <si>
+    <t>Sécurité sociale</t>
+  </si>
+  <si>
+    <t>4321</t>
+  </si>
+  <si>
+    <t>État, impôts sur les rémunérations</t>
+  </si>
+  <si>
+    <t>4221</t>
+  </si>
+  <si>
+    <t>Personnel, rémunérations dues</t>
+  </si>
+  <si>
+    <t>PAIE-2026-07-CMU0C857/P2</t>
+  </si>
+  <si>
+    <t>6612</t>
+  </si>
+  <si>
+    <t>Salaires des employés</t>
+  </si>
+  <si>
+    <t>PAIE-2026-07-CMU0C857/P3</t>
+  </si>
+  <si>
+    <t>PAIE-2026-07-CMU0C857/P4</t>
+  </si>
+  <si>
+    <t>6611</t>
+  </si>
+  <si>
+    <t>Salaires des ouvriers</t>
+  </si>
+  <si>
+    <t>PAIE-2026-07-CMU0C857/P5</t>
+  </si>
+  <si>
+    <t>PAIE-2026-07-CMU0C857/P6</t>
+  </si>
+  <si>
+    <t>PAIE-2026-07-CMU0C857/BQ</t>
+  </si>
+  <si>
+    <t>5211</t>
+  </si>
+  <si>
+    <t>Banques</t>
+  </si>
+  <si>
+    <t>31/08/2026</t>
+  </si>
+  <si>
+    <t>PAIE-2026-08-CMU0C857/P1</t>
+  </si>
+  <si>
+    <t>PAIE-2026-08-CMU0C857/P2</t>
+  </si>
+  <si>
+    <t>PAIE-2026-08-CMU0C857/P3</t>
+  </si>
+  <si>
+    <t>PAIE-2026-08-CMU0C857/P4</t>
+  </si>
+  <si>
+    <t>PAIE-2026-08-CMU0C857/P5</t>
+  </si>
+  <si>
+    <t>PAIE-2026-08-CMU0C857/P6</t>
+  </si>
+  <si>
+    <t>PAIE-2026-08-CMU0C857/BQ</t>
+  </si>
+  <si>
+    <t>PAIE-2026-08-CMU0C857-R2/P1</t>
+  </si>
+  <si>
+    <t>PAIE-2026-08-CMU0C857-R2/P2</t>
+  </si>
+  <si>
+    <t>PAIE-2026-08-CMU0C857-R2/P3</t>
+  </si>
+  <si>
+    <t>PAIE-2026-08-CMU0C857-R2/P4</t>
+  </si>
+  <si>
+    <t>PAIE-2026-08-CMU0C857-R2/P5</t>
+  </si>
+  <si>
+    <t>PAIE-2026-08-CMU0C857-R2/P6</t>
+  </si>
+  <si>
+    <t>PAIE-2026-08-CMU0C857-R2/BQ</t>
+  </si>
+  <si>
     <t>05/09/2026</t>
   </si>
   <si>
@@ -128,6 +245,30 @@
   </si>
   <si>
     <t>Charges de personnel</t>
+  </si>
+  <si>
+    <t>15/09/2026</t>
+  </si>
+  <si>
+    <t>PAIE-REV-2026-08-CMU0C857/P1</t>
+  </si>
+  <si>
+    <t>PAIE-REV-2026-08-CMU0C857/P2</t>
+  </si>
+  <si>
+    <t>PAIE-REV-2026-08-CMU0C857/P3</t>
+  </si>
+  <si>
+    <t>PAIE-REV-2026-08-CMU0C857/P4</t>
+  </si>
+  <si>
+    <t>PAIE-REV-2026-08-CMU0C857/P5</t>
+  </si>
+  <si>
+    <t>PAIE-REV-2026-08-CMU0C857/P6</t>
+  </si>
+  <si>
+    <t>PAIE-REV-2026-08-CMU0C857/BQ</t>
   </si>
   <si>
     <t>Total journal PAIE</t>
@@ -712,7 +853,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F209"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1116,7 +1257,7 @@
         <v>38</v>
       </c>
       <c r="E26" s="6">
-        <v>4250000</v>
+        <v>1200000</v>
       </c>
       <c r="F26" s="6"/>
     </row>
@@ -1128,81 +1269,103 @@
         <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="D27" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6">
-        <v>4250000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E28" s="9">
-        <v>4250000</v>
-      </c>
-      <c r="F28" s="9">
-        <v>4250000</v>
+        <v>40</v>
+      </c>
+      <c r="E27" s="6">
+        <v>150000</v>
+      </c>
+      <c r="F27" s="6"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" t="s">
+        <v>41</v>
+      </c>
+      <c r="D28" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6">
+        <v>225600</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6">
+        <v>88410</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
+      <c r="A30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" t="s">
+        <v>46</v>
+      </c>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6">
+        <v>1035990</v>
+      </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>9</v>
-      </c>
+      <c r="A31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" t="s">
+        <v>48</v>
+      </c>
+      <c r="D31" t="s">
+        <v>49</v>
+      </c>
+      <c r="E31" s="6">
+        <v>850000</v>
+      </c>
+      <c r="F31" s="6"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="B32" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="D32" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E32" s="6">
-        <v>365800</v>
+        <v>106250</v>
       </c>
       <c r="F32" s="6"/>
     </row>
@@ -1214,33 +1377,33 @@
         <v>14</v>
       </c>
       <c r="C33" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D33" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E33" s="6"/>
       <c r="F33" s="6">
-        <v>365800</v>
+        <v>159800</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="C34" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D34" t="s">
-        <v>47</v>
-      </c>
-      <c r="E34" s="6">
-        <v>637200</v>
-      </c>
-      <c r="F34" s="6"/>
+        <v>44</v>
+      </c>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6">
+        <v>49395</v>
+      </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
@@ -1250,31 +1413,31 @@
         <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D35" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E35" s="6"/>
       <c r="F35" s="6">
-        <v>637200</v>
+        <v>747055</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B36" t="s">
+        <v>50</v>
+      </c>
+      <c r="C36" t="s">
         <v>48</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>49</v>
       </c>
-      <c r="D36" t="s">
-        <v>50</v>
-      </c>
       <c r="E36" s="6">
-        <v>545750</v>
+        <v>550000</v>
       </c>
       <c r="F36" s="6"/>
     </row>
@@ -1286,33 +1449,33 @@
         <v>14</v>
       </c>
       <c r="C37" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D37" t="s">
-        <v>44</v>
-      </c>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6">
-        <v>545750</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="E37" s="6">
+        <v>68750</v>
+      </c>
+      <c r="F37" s="6"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>14</v>
+      </c>
+      <c r="B38" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" t="s">
         <v>41</v>
       </c>
-      <c r="B38" t="s">
-        <v>51</v>
-      </c>
-      <c r="C38" t="s">
-        <v>17</v>
-      </c>
       <c r="D38" t="s">
-        <v>18</v>
-      </c>
-      <c r="E38" s="6">
-        <v>442500</v>
-      </c>
-      <c r="F38" s="6"/>
+        <v>42</v>
+      </c>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6">
+        <v>103400</v>
+      </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
@@ -1329,110 +1492,132 @@
       </c>
       <c r="E39" s="6"/>
       <c r="F39" s="6">
-        <v>442500</v>
+        <v>21285</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="B40" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="C40" t="s">
+        <v>45</v>
+      </c>
+      <c r="D40" t="s">
         <v>46</v>
       </c>
-      <c r="D40" t="s">
-        <v>47</v>
-      </c>
-      <c r="E40" s="6">
-        <v>925120</v>
-      </c>
-      <c r="F40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6">
+        <v>494065</v>
+      </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="B41" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="C41" t="s">
+        <v>52</v>
+      </c>
+      <c r="D41" t="s">
+        <v>53</v>
+      </c>
+      <c r="E41" s="6">
+        <v>420000</v>
+      </c>
+      <c r="F41" s="6"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>14</v>
+      </c>
+      <c r="B42" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42" t="s">
+        <v>39</v>
+      </c>
+      <c r="D42" t="s">
+        <v>40</v>
+      </c>
+      <c r="E42" s="6">
+        <v>52500</v>
+      </c>
+      <c r="F42" s="6"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>14</v>
+      </c>
+      <c r="B43" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" t="s">
+        <v>41</v>
+      </c>
+      <c r="D43" t="s">
+        <v>42</v>
+      </c>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6">
+        <v>78960</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>14</v>
+      </c>
+      <c r="B44" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" t="s">
         <v>43</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D44" t="s">
         <v>44</v>
       </c>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6">
-        <v>925120</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E42" s="9">
-        <v>2916370</v>
-      </c>
-      <c r="F42" s="9">
-        <v>2916370</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6">
+        <v>11927</v>
+      </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>9</v>
+      <c r="A45" t="s">
+        <v>14</v>
+      </c>
+      <c r="B45" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" t="s">
+        <v>45</v>
+      </c>
+      <c r="D45" t="s">
+        <v>46</v>
+      </c>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6">
+        <v>381613</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C46" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D46" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E46" s="6">
-        <v>327450</v>
+        <v>480000</v>
       </c>
       <c r="F46" s="6"/>
     </row>
@@ -1444,15 +1629,15 @@
         <v>14</v>
       </c>
       <c r="C47" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="D47" t="s">
-        <v>58</v>
-      </c>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6">
-        <v>277500</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="E47" s="6">
+        <v>60000</v>
+      </c>
+      <c r="F47" s="6"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
@@ -1462,22 +1647,22 @@
         <v>14</v>
       </c>
       <c r="C48" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="D48" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="E48" s="6"/>
       <c r="F48" s="6">
-        <v>49950</v>
+        <v>90240</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="B49" t="s">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="C49" t="s">
         <v>43</v>
@@ -1485,10 +1670,10 @@
       <c r="D49" t="s">
         <v>44</v>
       </c>
-      <c r="E49" s="6">
-        <v>608880</v>
-      </c>
-      <c r="F49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6">
+        <v>14738</v>
+      </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
@@ -1498,49 +1683,49 @@
         <v>14</v>
       </c>
       <c r="C50" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D50" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E50" s="6"/>
       <c r="F50" s="6">
-        <v>516000</v>
+        <v>435022</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="B51" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="D51" t="s">
-        <v>60</v>
-      </c>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6">
-        <v>92880</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="E51" s="6">
+        <v>750000</v>
+      </c>
+      <c r="F51" s="6"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="B52" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="C52" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D52" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E52" s="6">
-        <v>1220120</v>
+        <v>93750</v>
       </c>
       <c r="F52" s="6"/>
     </row>
@@ -1552,14 +1737,14 @@
         <v>14</v>
       </c>
       <c r="C53" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="D53" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="E53" s="6"/>
       <c r="F53" s="6">
-        <v>1034000</v>
+        <v>141000</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -1570,51 +1755,51 @@
         <v>14</v>
       </c>
       <c r="C54" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="D54" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="E54" s="6"/>
       <c r="F54" s="6">
-        <v>186120</v>
+        <v>40025</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="B55" t="s">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="C55" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D55" t="s">
-        <v>44</v>
-      </c>
-      <c r="E55" s="6">
-        <v>365800</v>
-      </c>
-      <c r="F55" s="6"/>
+        <v>46</v>
+      </c>
+      <c r="E55" s="6"/>
+      <c r="F55" s="6">
+        <v>662725</v>
+      </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="C56" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D56" t="s">
-        <v>58</v>
-      </c>
-      <c r="E56" s="6"/>
-      <c r="F56" s="6">
-        <v>310000</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="E56" s="6">
+        <v>3756470</v>
+      </c>
+      <c r="F56" s="6"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
@@ -1624,31 +1809,31 @@
         <v>14</v>
       </c>
       <c r="C57" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D57" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E57" s="6"/>
       <c r="F57" s="6">
-        <v>55800</v>
+        <v>3756470</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C58" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D58" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E58" s="6">
-        <v>637200</v>
+        <v>1200000</v>
       </c>
       <c r="F58" s="6"/>
     </row>
@@ -1660,15 +1845,15 @@
         <v>14</v>
       </c>
       <c r="C59" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="D59" t="s">
-        <v>58</v>
-      </c>
-      <c r="E59" s="6"/>
-      <c r="F59" s="6">
-        <v>540000</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="E59" s="6">
+        <v>150000</v>
+      </c>
+      <c r="F59" s="6"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
@@ -1678,22 +1863,22 @@
         <v>14</v>
       </c>
       <c r="C60" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="D60" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="E60" s="6"/>
       <c r="F60" s="6">
-        <v>97200</v>
+        <v>225600</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="B61" t="s">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="C61" t="s">
         <v>43</v>
@@ -1701,10 +1886,10 @@
       <c r="D61" t="s">
         <v>44</v>
       </c>
-      <c r="E61" s="6">
-        <v>545750</v>
-      </c>
-      <c r="F61" s="6"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="6">
+        <v>88410</v>
+      </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
@@ -1714,49 +1899,49 @@
         <v>14</v>
       </c>
       <c r="C62" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D62" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E62" s="6"/>
       <c r="F62" s="6">
-        <v>462500</v>
+        <v>1035990</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="B63" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="C63" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="D63" t="s">
-        <v>60</v>
-      </c>
-      <c r="E63" s="6"/>
-      <c r="F63" s="6">
-        <v>83250</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="E63" s="6">
+        <v>850000</v>
+      </c>
+      <c r="F63" s="6"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="B64" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="C64" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D64" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E64" s="6">
-        <v>1062000</v>
+        <v>106250</v>
       </c>
       <c r="F64" s="6"/>
     </row>
@@ -1768,14 +1953,14 @@
         <v>14</v>
       </c>
       <c r="C65" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="D65" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="E65" s="6"/>
       <c r="F65" s="6">
-        <v>900000</v>
+        <v>159800</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -1786,51 +1971,51 @@
         <v>14</v>
       </c>
       <c r="C66" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="D66" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="E66" s="6"/>
       <c r="F66" s="6">
-        <v>162000</v>
+        <v>49395</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="B67" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="C67" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D67" t="s">
-        <v>44</v>
-      </c>
-      <c r="E67" s="6">
-        <v>442500</v>
-      </c>
-      <c r="F67" s="6"/>
+        <v>46</v>
+      </c>
+      <c r="E67" s="6"/>
+      <c r="F67" s="6">
+        <v>747055</v>
+      </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="B68" t="s">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="C68" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="D68" t="s">
-        <v>74</v>
-      </c>
-      <c r="E68" s="6"/>
-      <c r="F68" s="6">
-        <v>375000</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="E68" s="6">
+        <v>550000</v>
+      </c>
+      <c r="F68" s="6"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
@@ -1840,33 +2025,33 @@
         <v>14</v>
       </c>
       <c r="C69" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="D69" t="s">
-        <v>60</v>
-      </c>
-      <c r="E69" s="6"/>
-      <c r="F69" s="6">
-        <v>67500</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="E69" s="6">
+        <v>68750</v>
+      </c>
+      <c r="F69" s="6"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="B70" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="C70" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D70" t="s">
-        <v>44</v>
-      </c>
-      <c r="E70" s="6">
-        <v>578200</v>
-      </c>
-      <c r="F70" s="6"/>
+        <v>42</v>
+      </c>
+      <c r="E70" s="6"/>
+      <c r="F70" s="6">
+        <v>103400</v>
+      </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
@@ -1876,14 +2061,14 @@
         <v>14</v>
       </c>
       <c r="C71" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="D71" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="E71" s="6"/>
       <c r="F71" s="6">
-        <v>490000</v>
+        <v>21285</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -1894,31 +2079,31 @@
         <v>14</v>
       </c>
       <c r="C72" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="D72" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="E72" s="6"/>
       <c r="F72" s="6">
-        <v>88200</v>
+        <v>494065</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B73" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="C73" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D73" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="E73" s="6">
-        <v>861400</v>
+        <v>420000</v>
       </c>
       <c r="F73" s="6"/>
     </row>
@@ -1930,15 +2115,15 @@
         <v>14</v>
       </c>
       <c r="C74" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="D74" t="s">
-        <v>74</v>
-      </c>
-      <c r="E74" s="6"/>
-      <c r="F74" s="6">
-        <v>730000</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="E74" s="6">
+        <v>52500</v>
+      </c>
+      <c r="F74" s="6"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
@@ -1948,22 +2133,22 @@
         <v>14</v>
       </c>
       <c r="C75" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="D75" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="E75" s="6"/>
       <c r="F75" s="6">
-        <v>131400</v>
+        <v>78960</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="B76" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="C76" t="s">
         <v>43</v>
@@ -1971,10 +2156,10 @@
       <c r="D76" t="s">
         <v>44</v>
       </c>
-      <c r="E76" s="6">
-        <v>925120</v>
-      </c>
-      <c r="F76" s="6"/>
+      <c r="E76" s="6"/>
+      <c r="F76" s="6">
+        <v>11927</v>
+      </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
@@ -1984,57 +2169,2317 @@
         <v>14</v>
       </c>
       <c r="C77" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D77" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E77" s="6"/>
       <c r="F77" s="6">
-        <v>784000</v>
+        <v>381613</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="B78" t="s">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="C78" t="s">
+        <v>48</v>
+      </c>
+      <c r="D78" t="s">
+        <v>49</v>
+      </c>
+      <c r="E78" s="6">
+        <v>480000</v>
+      </c>
+      <c r="F78" s="6"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>14</v>
+      </c>
+      <c r="B79" t="s">
+        <v>14</v>
+      </c>
+      <c r="C79" t="s">
+        <v>39</v>
+      </c>
+      <c r="D79" t="s">
+        <v>40</v>
+      </c>
+      <c r="E79" s="6">
+        <v>60000</v>
+      </c>
+      <c r="F79" s="6"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>14</v>
+      </c>
+      <c r="B80" t="s">
+        <v>14</v>
+      </c>
+      <c r="C80" t="s">
+        <v>41</v>
+      </c>
+      <c r="D80" t="s">
+        <v>42</v>
+      </c>
+      <c r="E80" s="6"/>
+      <c r="F80" s="6">
+        <v>90240</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>14</v>
+      </c>
+      <c r="B81" t="s">
+        <v>14</v>
+      </c>
+      <c r="C81" t="s">
+        <v>43</v>
+      </c>
+      <c r="D81" t="s">
+        <v>44</v>
+      </c>
+      <c r="E81" s="6"/>
+      <c r="F81" s="6">
+        <v>14738</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>14</v>
+      </c>
+      <c r="B82" t="s">
+        <v>14</v>
+      </c>
+      <c r="C82" t="s">
+        <v>45</v>
+      </c>
+      <c r="D82" t="s">
+        <v>46</v>
+      </c>
+      <c r="E82" s="6"/>
+      <c r="F82" s="6">
+        <v>435022</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
         <v>59</v>
       </c>
-      <c r="D78" t="s">
-        <v>60</v>
-      </c>
-      <c r="E78" s="6"/>
-      <c r="F78" s="6">
+      <c r="B83" t="s">
+        <v>65</v>
+      </c>
+      <c r="C83" t="s">
+        <v>48</v>
+      </c>
+      <c r="D83" t="s">
+        <v>49</v>
+      </c>
+      <c r="E83" s="6">
+        <v>750000</v>
+      </c>
+      <c r="F83" s="6"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>14</v>
+      </c>
+      <c r="B84" t="s">
+        <v>14</v>
+      </c>
+      <c r="C84" t="s">
+        <v>39</v>
+      </c>
+      <c r="D84" t="s">
+        <v>40</v>
+      </c>
+      <c r="E84" s="6">
+        <v>93750</v>
+      </c>
+      <c r="F84" s="6"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>14</v>
+      </c>
+      <c r="B85" t="s">
+        <v>14</v>
+      </c>
+      <c r="C85" t="s">
+        <v>41</v>
+      </c>
+      <c r="D85" t="s">
+        <v>42</v>
+      </c>
+      <c r="E85" s="6"/>
+      <c r="F85" s="6">
+        <v>141000</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>14</v>
+      </c>
+      <c r="B86" t="s">
+        <v>14</v>
+      </c>
+      <c r="C86" t="s">
+        <v>43</v>
+      </c>
+      <c r="D86" t="s">
+        <v>44</v>
+      </c>
+      <c r="E86" s="6"/>
+      <c r="F86" s="6">
+        <v>40025</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>14</v>
+      </c>
+      <c r="B87" t="s">
+        <v>14</v>
+      </c>
+      <c r="C87" t="s">
+        <v>45</v>
+      </c>
+      <c r="D87" t="s">
+        <v>46</v>
+      </c>
+      <c r="E87" s="6"/>
+      <c r="F87" s="6">
+        <v>662725</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>59</v>
+      </c>
+      <c r="B88" t="s">
+        <v>66</v>
+      </c>
+      <c r="C88" t="s">
+        <v>45</v>
+      </c>
+      <c r="D88" t="s">
+        <v>46</v>
+      </c>
+      <c r="E88" s="6">
+        <v>3756470</v>
+      </c>
+      <c r="F88" s="6"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>14</v>
+      </c>
+      <c r="B89" t="s">
+        <v>14</v>
+      </c>
+      <c r="C89" t="s">
+        <v>57</v>
+      </c>
+      <c r="D89" t="s">
+        <v>58</v>
+      </c>
+      <c r="E89" s="6"/>
+      <c r="F89" s="6">
+        <v>3756470</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>59</v>
+      </c>
+      <c r="B90" t="s">
+        <v>67</v>
+      </c>
+      <c r="C90" t="s">
+        <v>37</v>
+      </c>
+      <c r="D90" t="s">
+        <v>38</v>
+      </c>
+      <c r="E90" s="6">
+        <v>1200000</v>
+      </c>
+      <c r="F90" s="6"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>14</v>
+      </c>
+      <c r="B91" t="s">
+        <v>14</v>
+      </c>
+      <c r="C91" t="s">
+        <v>39</v>
+      </c>
+      <c r="D91" t="s">
+        <v>40</v>
+      </c>
+      <c r="E91" s="6">
+        <v>150000</v>
+      </c>
+      <c r="F91" s="6"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>14</v>
+      </c>
+      <c r="B92" t="s">
+        <v>14</v>
+      </c>
+      <c r="C92" t="s">
+        <v>41</v>
+      </c>
+      <c r="D92" t="s">
+        <v>42</v>
+      </c>
+      <c r="E92" s="6"/>
+      <c r="F92" s="6">
+        <v>225600</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>14</v>
+      </c>
+      <c r="B93" t="s">
+        <v>14</v>
+      </c>
+      <c r="C93" t="s">
+        <v>43</v>
+      </c>
+      <c r="D93" t="s">
+        <v>44</v>
+      </c>
+      <c r="E93" s="6"/>
+      <c r="F93" s="6">
+        <v>88410</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>14</v>
+      </c>
+      <c r="B94" t="s">
+        <v>14</v>
+      </c>
+      <c r="C94" t="s">
+        <v>45</v>
+      </c>
+      <c r="D94" t="s">
+        <v>46</v>
+      </c>
+      <c r="E94" s="6"/>
+      <c r="F94" s="6">
+        <v>1035990</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>59</v>
+      </c>
+      <c r="B95" t="s">
+        <v>68</v>
+      </c>
+      <c r="C95" t="s">
+        <v>48</v>
+      </c>
+      <c r="D95" t="s">
+        <v>49</v>
+      </c>
+      <c r="E95" s="6">
+        <v>850000</v>
+      </c>
+      <c r="F95" s="6"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>14</v>
+      </c>
+      <c r="B96" t="s">
+        <v>14</v>
+      </c>
+      <c r="C96" t="s">
+        <v>39</v>
+      </c>
+      <c r="D96" t="s">
+        <v>40</v>
+      </c>
+      <c r="E96" s="6">
+        <v>106250</v>
+      </c>
+      <c r="F96" s="6"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>14</v>
+      </c>
+      <c r="B97" t="s">
+        <v>14</v>
+      </c>
+      <c r="C97" t="s">
+        <v>41</v>
+      </c>
+      <c r="D97" t="s">
+        <v>42</v>
+      </c>
+      <c r="E97" s="6"/>
+      <c r="F97" s="6">
+        <v>159800</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>14</v>
+      </c>
+      <c r="B98" t="s">
+        <v>14</v>
+      </c>
+      <c r="C98" t="s">
+        <v>43</v>
+      </c>
+      <c r="D98" t="s">
+        <v>44</v>
+      </c>
+      <c r="E98" s="6"/>
+      <c r="F98" s="6">
+        <v>49395</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>14</v>
+      </c>
+      <c r="B99" t="s">
+        <v>14</v>
+      </c>
+      <c r="C99" t="s">
+        <v>45</v>
+      </c>
+      <c r="D99" t="s">
+        <v>46</v>
+      </c>
+      <c r="E99" s="6"/>
+      <c r="F99" s="6">
+        <v>747055</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>59</v>
+      </c>
+      <c r="B100" t="s">
+        <v>69</v>
+      </c>
+      <c r="C100" t="s">
+        <v>48</v>
+      </c>
+      <c r="D100" t="s">
+        <v>49</v>
+      </c>
+      <c r="E100" s="6">
+        <v>550000</v>
+      </c>
+      <c r="F100" s="6"/>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>14</v>
+      </c>
+      <c r="B101" t="s">
+        <v>14</v>
+      </c>
+      <c r="C101" t="s">
+        <v>39</v>
+      </c>
+      <c r="D101" t="s">
+        <v>40</v>
+      </c>
+      <c r="E101" s="6">
+        <v>68750</v>
+      </c>
+      <c r="F101" s="6"/>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>14</v>
+      </c>
+      <c r="B102" t="s">
+        <v>14</v>
+      </c>
+      <c r="C102" t="s">
+        <v>41</v>
+      </c>
+      <c r="D102" t="s">
+        <v>42</v>
+      </c>
+      <c r="E102" s="6"/>
+      <c r="F102" s="6">
+        <v>103400</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>14</v>
+      </c>
+      <c r="B103" t="s">
+        <v>14</v>
+      </c>
+      <c r="C103" t="s">
+        <v>43</v>
+      </c>
+      <c r="D103" t="s">
+        <v>44</v>
+      </c>
+      <c r="E103" s="6"/>
+      <c r="F103" s="6">
+        <v>21285</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>14</v>
+      </c>
+      <c r="B104" t="s">
+        <v>14</v>
+      </c>
+      <c r="C104" t="s">
+        <v>45</v>
+      </c>
+      <c r="D104" t="s">
+        <v>46</v>
+      </c>
+      <c r="E104" s="6"/>
+      <c r="F104" s="6">
+        <v>494065</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>59</v>
+      </c>
+      <c r="B105" t="s">
+        <v>70</v>
+      </c>
+      <c r="C105" t="s">
+        <v>52</v>
+      </c>
+      <c r="D105" t="s">
+        <v>53</v>
+      </c>
+      <c r="E105" s="6">
+        <v>420000</v>
+      </c>
+      <c r="F105" s="6"/>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>14</v>
+      </c>
+      <c r="B106" t="s">
+        <v>14</v>
+      </c>
+      <c r="C106" t="s">
+        <v>39</v>
+      </c>
+      <c r="D106" t="s">
+        <v>40</v>
+      </c>
+      <c r="E106" s="6">
+        <v>52500</v>
+      </c>
+      <c r="F106" s="6"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>14</v>
+      </c>
+      <c r="B107" t="s">
+        <v>14</v>
+      </c>
+      <c r="C107" t="s">
+        <v>41</v>
+      </c>
+      <c r="D107" t="s">
+        <v>42</v>
+      </c>
+      <c r="E107" s="6"/>
+      <c r="F107" s="6">
+        <v>78960</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>14</v>
+      </c>
+      <c r="B108" t="s">
+        <v>14</v>
+      </c>
+      <c r="C108" t="s">
+        <v>43</v>
+      </c>
+      <c r="D108" t="s">
+        <v>44</v>
+      </c>
+      <c r="E108" s="6"/>
+      <c r="F108" s="6">
+        <v>11927</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>14</v>
+      </c>
+      <c r="B109" t="s">
+        <v>14</v>
+      </c>
+      <c r="C109" t="s">
+        <v>45</v>
+      </c>
+      <c r="D109" t="s">
+        <v>46</v>
+      </c>
+      <c r="E109" s="6"/>
+      <c r="F109" s="6">
+        <v>381613</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>59</v>
+      </c>
+      <c r="B110" t="s">
+        <v>71</v>
+      </c>
+      <c r="C110" t="s">
+        <v>48</v>
+      </c>
+      <c r="D110" t="s">
+        <v>49</v>
+      </c>
+      <c r="E110" s="6">
+        <v>480000</v>
+      </c>
+      <c r="F110" s="6"/>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>14</v>
+      </c>
+      <c r="B111" t="s">
+        <v>14</v>
+      </c>
+      <c r="C111" t="s">
+        <v>39</v>
+      </c>
+      <c r="D111" t="s">
+        <v>40</v>
+      </c>
+      <c r="E111" s="6">
+        <v>60000</v>
+      </c>
+      <c r="F111" s="6"/>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>14</v>
+      </c>
+      <c r="B112" t="s">
+        <v>14</v>
+      </c>
+      <c r="C112" t="s">
+        <v>41</v>
+      </c>
+      <c r="D112" t="s">
+        <v>42</v>
+      </c>
+      <c r="E112" s="6"/>
+      <c r="F112" s="6">
+        <v>90240</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>14</v>
+      </c>
+      <c r="B113" t="s">
+        <v>14</v>
+      </c>
+      <c r="C113" t="s">
+        <v>43</v>
+      </c>
+      <c r="D113" t="s">
+        <v>44</v>
+      </c>
+      <c r="E113" s="6"/>
+      <c r="F113" s="6">
+        <v>14738</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>14</v>
+      </c>
+      <c r="B114" t="s">
+        <v>14</v>
+      </c>
+      <c r="C114" t="s">
+        <v>45</v>
+      </c>
+      <c r="D114" t="s">
+        <v>46</v>
+      </c>
+      <c r="E114" s="6"/>
+      <c r="F114" s="6">
+        <v>435022</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>59</v>
+      </c>
+      <c r="B115" t="s">
+        <v>72</v>
+      </c>
+      <c r="C115" t="s">
+        <v>48</v>
+      </c>
+      <c r="D115" t="s">
+        <v>49</v>
+      </c>
+      <c r="E115" s="6">
+        <v>750000</v>
+      </c>
+      <c r="F115" s="6"/>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>14</v>
+      </c>
+      <c r="B116" t="s">
+        <v>14</v>
+      </c>
+      <c r="C116" t="s">
+        <v>39</v>
+      </c>
+      <c r="D116" t="s">
+        <v>40</v>
+      </c>
+      <c r="E116" s="6">
+        <v>93750</v>
+      </c>
+      <c r="F116" s="6"/>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>14</v>
+      </c>
+      <c r="B117" t="s">
+        <v>14</v>
+      </c>
+      <c r="C117" t="s">
+        <v>41</v>
+      </c>
+      <c r="D117" t="s">
+        <v>42</v>
+      </c>
+      <c r="E117" s="6"/>
+      <c r="F117" s="6">
+        <v>141000</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>14</v>
+      </c>
+      <c r="B118" t="s">
+        <v>14</v>
+      </c>
+      <c r="C118" t="s">
+        <v>43</v>
+      </c>
+      <c r="D118" t="s">
+        <v>44</v>
+      </c>
+      <c r="E118" s="6"/>
+      <c r="F118" s="6">
+        <v>40025</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>14</v>
+      </c>
+      <c r="B119" t="s">
+        <v>14</v>
+      </c>
+      <c r="C119" t="s">
+        <v>45</v>
+      </c>
+      <c r="D119" t="s">
+        <v>46</v>
+      </c>
+      <c r="E119" s="6"/>
+      <c r="F119" s="6">
+        <v>662725</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>59</v>
+      </c>
+      <c r="B120" t="s">
+        <v>73</v>
+      </c>
+      <c r="C120" t="s">
+        <v>45</v>
+      </c>
+      <c r="D120" t="s">
+        <v>46</v>
+      </c>
+      <c r="E120" s="6">
+        <v>3756470</v>
+      </c>
+      <c r="F120" s="6"/>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>14</v>
+      </c>
+      <c r="B121" t="s">
+        <v>14</v>
+      </c>
+      <c r="C121" t="s">
+        <v>57</v>
+      </c>
+      <c r="D121" t="s">
+        <v>58</v>
+      </c>
+      <c r="E121" s="6"/>
+      <c r="F121" s="6">
+        <v>3756470</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>74</v>
+      </c>
+      <c r="B122" t="s">
+        <v>75</v>
+      </c>
+      <c r="C122" t="s">
+        <v>76</v>
+      </c>
+      <c r="D122" t="s">
+        <v>77</v>
+      </c>
+      <c r="E122" s="6">
+        <v>4250000</v>
+      </c>
+      <c r="F122" s="6"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>14</v>
+      </c>
+      <c r="B123" t="s">
+        <v>14</v>
+      </c>
+      <c r="C123" t="s">
+        <v>17</v>
+      </c>
+      <c r="D123" t="s">
+        <v>18</v>
+      </c>
+      <c r="E123" s="6"/>
+      <c r="F123" s="6">
+        <v>4250000</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>78</v>
+      </c>
+      <c r="B124" t="s">
+        <v>79</v>
+      </c>
+      <c r="C124" t="s">
+        <v>41</v>
+      </c>
+      <c r="D124" t="s">
+        <v>42</v>
+      </c>
+      <c r="E124" s="6">
+        <v>225600</v>
+      </c>
+      <c r="F124" s="6"/>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>14</v>
+      </c>
+      <c r="B125" t="s">
+        <v>14</v>
+      </c>
+      <c r="C125" t="s">
+        <v>43</v>
+      </c>
+      <c r="D125" t="s">
+        <v>44</v>
+      </c>
+      <c r="E125" s="6">
+        <v>88410</v>
+      </c>
+      <c r="F125" s="6"/>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>14</v>
+      </c>
+      <c r="B126" t="s">
+        <v>14</v>
+      </c>
+      <c r="C126" t="s">
+        <v>45</v>
+      </c>
+      <c r="D126" t="s">
+        <v>46</v>
+      </c>
+      <c r="E126" s="6">
+        <v>1035990</v>
+      </c>
+      <c r="F126" s="6"/>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>14</v>
+      </c>
+      <c r="B127" t="s">
+        <v>14</v>
+      </c>
+      <c r="C127" t="s">
+        <v>37</v>
+      </c>
+      <c r="D127" t="s">
+        <v>38</v>
+      </c>
+      <c r="E127" s="6"/>
+      <c r="F127" s="6">
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>14</v>
+      </c>
+      <c r="B128" t="s">
+        <v>14</v>
+      </c>
+      <c r="C128" t="s">
+        <v>39</v>
+      </c>
+      <c r="D128" t="s">
+        <v>40</v>
+      </c>
+      <c r="E128" s="6"/>
+      <c r="F128" s="6">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>78</v>
+      </c>
+      <c r="B129" t="s">
+        <v>80</v>
+      </c>
+      <c r="C129" t="s">
+        <v>41</v>
+      </c>
+      <c r="D129" t="s">
+        <v>42</v>
+      </c>
+      <c r="E129" s="6">
+        <v>159800</v>
+      </c>
+      <c r="F129" s="6"/>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>14</v>
+      </c>
+      <c r="B130" t="s">
+        <v>14</v>
+      </c>
+      <c r="C130" t="s">
+        <v>43</v>
+      </c>
+      <c r="D130" t="s">
+        <v>44</v>
+      </c>
+      <c r="E130" s="6">
+        <v>49395</v>
+      </c>
+      <c r="F130" s="6"/>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>14</v>
+      </c>
+      <c r="B131" t="s">
+        <v>14</v>
+      </c>
+      <c r="C131" t="s">
+        <v>45</v>
+      </c>
+      <c r="D131" t="s">
+        <v>46</v>
+      </c>
+      <c r="E131" s="6">
+        <v>747055</v>
+      </c>
+      <c r="F131" s="6"/>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>14</v>
+      </c>
+      <c r="B132" t="s">
+        <v>14</v>
+      </c>
+      <c r="C132" t="s">
+        <v>48</v>
+      </c>
+      <c r="D132" t="s">
+        <v>49</v>
+      </c>
+      <c r="E132" s="6"/>
+      <c r="F132" s="6">
+        <v>850000</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>14</v>
+      </c>
+      <c r="B133" t="s">
+        <v>14</v>
+      </c>
+      <c r="C133" t="s">
+        <v>39</v>
+      </c>
+      <c r="D133" t="s">
+        <v>40</v>
+      </c>
+      <c r="E133" s="6"/>
+      <c r="F133" s="6">
+        <v>106250</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>78</v>
+      </c>
+      <c r="B134" t="s">
+        <v>81</v>
+      </c>
+      <c r="C134" t="s">
+        <v>41</v>
+      </c>
+      <c r="D134" t="s">
+        <v>42</v>
+      </c>
+      <c r="E134" s="6">
+        <v>103400</v>
+      </c>
+      <c r="F134" s="6"/>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>14</v>
+      </c>
+      <c r="B135" t="s">
+        <v>14</v>
+      </c>
+      <c r="C135" t="s">
+        <v>43</v>
+      </c>
+      <c r="D135" t="s">
+        <v>44</v>
+      </c>
+      <c r="E135" s="6">
+        <v>21285</v>
+      </c>
+      <c r="F135" s="6"/>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>14</v>
+      </c>
+      <c r="B136" t="s">
+        <v>14</v>
+      </c>
+      <c r="C136" t="s">
+        <v>45</v>
+      </c>
+      <c r="D136" t="s">
+        <v>46</v>
+      </c>
+      <c r="E136" s="6">
+        <v>494065</v>
+      </c>
+      <c r="F136" s="6"/>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>14</v>
+      </c>
+      <c r="B137" t="s">
+        <v>14</v>
+      </c>
+      <c r="C137" t="s">
+        <v>48</v>
+      </c>
+      <c r="D137" t="s">
+        <v>49</v>
+      </c>
+      <c r="E137" s="6"/>
+      <c r="F137" s="6">
+        <v>550000</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>14</v>
+      </c>
+      <c r="B138" t="s">
+        <v>14</v>
+      </c>
+      <c r="C138" t="s">
+        <v>39</v>
+      </c>
+      <c r="D138" t="s">
+        <v>40</v>
+      </c>
+      <c r="E138" s="6"/>
+      <c r="F138" s="6">
+        <v>68750</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>78</v>
+      </c>
+      <c r="B139" t="s">
+        <v>82</v>
+      </c>
+      <c r="C139" t="s">
+        <v>41</v>
+      </c>
+      <c r="D139" t="s">
+        <v>42</v>
+      </c>
+      <c r="E139" s="6">
+        <v>78960</v>
+      </c>
+      <c r="F139" s="6"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>14</v>
+      </c>
+      <c r="B140" t="s">
+        <v>14</v>
+      </c>
+      <c r="C140" t="s">
+        <v>43</v>
+      </c>
+      <c r="D140" t="s">
+        <v>44</v>
+      </c>
+      <c r="E140" s="6">
+        <v>11927</v>
+      </c>
+      <c r="F140" s="6"/>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>14</v>
+      </c>
+      <c r="B141" t="s">
+        <v>14</v>
+      </c>
+      <c r="C141" t="s">
+        <v>45</v>
+      </c>
+      <c r="D141" t="s">
+        <v>46</v>
+      </c>
+      <c r="E141" s="6">
+        <v>381613</v>
+      </c>
+      <c r="F141" s="6"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>14</v>
+      </c>
+      <c r="B142" t="s">
+        <v>14</v>
+      </c>
+      <c r="C142" t="s">
+        <v>52</v>
+      </c>
+      <c r="D142" t="s">
+        <v>53</v>
+      </c>
+      <c r="E142" s="6"/>
+      <c r="F142" s="6">
+        <v>420000</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>14</v>
+      </c>
+      <c r="B143" t="s">
+        <v>14</v>
+      </c>
+      <c r="C143" t="s">
+        <v>39</v>
+      </c>
+      <c r="D143" t="s">
+        <v>40</v>
+      </c>
+      <c r="E143" s="6"/>
+      <c r="F143" s="6">
+        <v>52500</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>78</v>
+      </c>
+      <c r="B144" t="s">
+        <v>83</v>
+      </c>
+      <c r="C144" t="s">
+        <v>41</v>
+      </c>
+      <c r="D144" t="s">
+        <v>42</v>
+      </c>
+      <c r="E144" s="6">
+        <v>90240</v>
+      </c>
+      <c r="F144" s="6"/>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>14</v>
+      </c>
+      <c r="B145" t="s">
+        <v>14</v>
+      </c>
+      <c r="C145" t="s">
+        <v>43</v>
+      </c>
+      <c r="D145" t="s">
+        <v>44</v>
+      </c>
+      <c r="E145" s="6">
+        <v>14738</v>
+      </c>
+      <c r="F145" s="6"/>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>14</v>
+      </c>
+      <c r="B146" t="s">
+        <v>14</v>
+      </c>
+      <c r="C146" t="s">
+        <v>45</v>
+      </c>
+      <c r="D146" t="s">
+        <v>46</v>
+      </c>
+      <c r="E146" s="6">
+        <v>435022</v>
+      </c>
+      <c r="F146" s="6"/>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>14</v>
+      </c>
+      <c r="B147" t="s">
+        <v>14</v>
+      </c>
+      <c r="C147" t="s">
+        <v>48</v>
+      </c>
+      <c r="D147" t="s">
+        <v>49</v>
+      </c>
+      <c r="E147" s="6"/>
+      <c r="F147" s="6">
+        <v>480000</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>14</v>
+      </c>
+      <c r="B148" t="s">
+        <v>14</v>
+      </c>
+      <c r="C148" t="s">
+        <v>39</v>
+      </c>
+      <c r="D148" t="s">
+        <v>40</v>
+      </c>
+      <c r="E148" s="6"/>
+      <c r="F148" s="6">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>78</v>
+      </c>
+      <c r="B149" t="s">
+        <v>84</v>
+      </c>
+      <c r="C149" t="s">
+        <v>41</v>
+      </c>
+      <c r="D149" t="s">
+        <v>42</v>
+      </c>
+      <c r="E149" s="6">
+        <v>141000</v>
+      </c>
+      <c r="F149" s="6"/>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>14</v>
+      </c>
+      <c r="B150" t="s">
+        <v>14</v>
+      </c>
+      <c r="C150" t="s">
+        <v>43</v>
+      </c>
+      <c r="D150" t="s">
+        <v>44</v>
+      </c>
+      <c r="E150" s="6">
+        <v>40025</v>
+      </c>
+      <c r="F150" s="6"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>14</v>
+      </c>
+      <c r="B151" t="s">
+        <v>14</v>
+      </c>
+      <c r="C151" t="s">
+        <v>45</v>
+      </c>
+      <c r="D151" t="s">
+        <v>46</v>
+      </c>
+      <c r="E151" s="6">
+        <v>662725</v>
+      </c>
+      <c r="F151" s="6"/>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>14</v>
+      </c>
+      <c r="B152" t="s">
+        <v>14</v>
+      </c>
+      <c r="C152" t="s">
+        <v>48</v>
+      </c>
+      <c r="D152" t="s">
+        <v>49</v>
+      </c>
+      <c r="E152" s="6"/>
+      <c r="F152" s="6">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>14</v>
+      </c>
+      <c r="B153" t="s">
+        <v>14</v>
+      </c>
+      <c r="C153" t="s">
+        <v>39</v>
+      </c>
+      <c r="D153" t="s">
+        <v>40</v>
+      </c>
+      <c r="E153" s="6"/>
+      <c r="F153" s="6">
+        <v>93750</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>78</v>
+      </c>
+      <c r="B154" t="s">
+        <v>85</v>
+      </c>
+      <c r="C154" t="s">
+        <v>57</v>
+      </c>
+      <c r="D154" t="s">
+        <v>58</v>
+      </c>
+      <c r="E154" s="6">
+        <v>3756470</v>
+      </c>
+      <c r="F154" s="6"/>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>14</v>
+      </c>
+      <c r="B155" t="s">
+        <v>14</v>
+      </c>
+      <c r="C155" t="s">
+        <v>45</v>
+      </c>
+      <c r="D155" t="s">
+        <v>46</v>
+      </c>
+      <c r="E155" s="6"/>
+      <c r="F155" s="6">
+        <v>3756470</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B156" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C156" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D156" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="E156" s="9">
+        <v>38400880</v>
+      </c>
+      <c r="F156" s="9">
+        <v>38400880</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B158" s="4"/>
+      <c r="C158" s="4"/>
+      <c r="D158" s="4"/>
+      <c r="E158" s="4"/>
+      <c r="F158" s="4"/>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C159" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D159" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E159" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F159" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>88</v>
+      </c>
+      <c r="B160" t="s">
+        <v>89</v>
+      </c>
+      <c r="C160" t="s">
+        <v>17</v>
+      </c>
+      <c r="D160" t="s">
+        <v>18</v>
+      </c>
+      <c r="E160" s="6">
+        <v>365800</v>
+      </c>
+      <c r="F160" s="6"/>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>14</v>
+      </c>
+      <c r="B161" t="s">
+        <v>14</v>
+      </c>
+      <c r="C161" t="s">
+        <v>90</v>
+      </c>
+      <c r="D161" t="s">
+        <v>91</v>
+      </c>
+      <c r="E161" s="6"/>
+      <c r="F161" s="6">
+        <v>365800</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>88</v>
+      </c>
+      <c r="B162" t="s">
+        <v>92</v>
+      </c>
+      <c r="C162" t="s">
+        <v>93</v>
+      </c>
+      <c r="D162" t="s">
+        <v>94</v>
+      </c>
+      <c r="E162" s="6">
+        <v>637200</v>
+      </c>
+      <c r="F162" s="6"/>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>14</v>
+      </c>
+      <c r="B163" t="s">
+        <v>14</v>
+      </c>
+      <c r="C163" t="s">
+        <v>90</v>
+      </c>
+      <c r="D163" t="s">
+        <v>91</v>
+      </c>
+      <c r="E163" s="6"/>
+      <c r="F163" s="6">
+        <v>637200</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>88</v>
+      </c>
+      <c r="B164" t="s">
+        <v>95</v>
+      </c>
+      <c r="C164" t="s">
+        <v>96</v>
+      </c>
+      <c r="D164" t="s">
+        <v>97</v>
+      </c>
+      <c r="E164" s="6">
+        <v>545750</v>
+      </c>
+      <c r="F164" s="6"/>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>14</v>
+      </c>
+      <c r="B165" t="s">
+        <v>14</v>
+      </c>
+      <c r="C165" t="s">
+        <v>90</v>
+      </c>
+      <c r="D165" t="s">
+        <v>91</v>
+      </c>
+      <c r="E165" s="6"/>
+      <c r="F165" s="6">
+        <v>545750</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>88</v>
+      </c>
+      <c r="B166" t="s">
+        <v>98</v>
+      </c>
+      <c r="C166" t="s">
+        <v>17</v>
+      </c>
+      <c r="D166" t="s">
+        <v>18</v>
+      </c>
+      <c r="E166" s="6">
+        <v>442500</v>
+      </c>
+      <c r="F166" s="6"/>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>14</v>
+      </c>
+      <c r="B167" t="s">
+        <v>14</v>
+      </c>
+      <c r="C167" t="s">
+        <v>90</v>
+      </c>
+      <c r="D167" t="s">
+        <v>91</v>
+      </c>
+      <c r="E167" s="6"/>
+      <c r="F167" s="6">
+        <v>442500</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>88</v>
+      </c>
+      <c r="B168" t="s">
+        <v>99</v>
+      </c>
+      <c r="C168" t="s">
+        <v>93</v>
+      </c>
+      <c r="D168" t="s">
+        <v>94</v>
+      </c>
+      <c r="E168" s="6">
+        <v>925120</v>
+      </c>
+      <c r="F168" s="6"/>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>14</v>
+      </c>
+      <c r="B169" t="s">
+        <v>14</v>
+      </c>
+      <c r="C169" t="s">
+        <v>90</v>
+      </c>
+      <c r="D169" t="s">
+        <v>91</v>
+      </c>
+      <c r="E169" s="6"/>
+      <c r="F169" s="6">
+        <v>925120</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B170" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C170" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D170" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E170" s="9">
+        <v>2916370</v>
+      </c>
+      <c r="F170" s="9">
+        <v>2916370</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A172" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B172" s="4"/>
+      <c r="C172" s="4"/>
+      <c r="D172" s="4"/>
+      <c r="E172" s="4"/>
+      <c r="F172" s="4"/>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A173" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C173" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D173" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E173" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F173" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>102</v>
+      </c>
+      <c r="B174" t="s">
+        <v>103</v>
+      </c>
+      <c r="C174" t="s">
+        <v>90</v>
+      </c>
+      <c r="D174" t="s">
+        <v>91</v>
+      </c>
+      <c r="E174" s="6">
+        <v>327450</v>
+      </c>
+      <c r="F174" s="6"/>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>14</v>
+      </c>
+      <c r="B175" t="s">
+        <v>14</v>
+      </c>
+      <c r="C175" t="s">
+        <v>104</v>
+      </c>
+      <c r="D175" t="s">
+        <v>105</v>
+      </c>
+      <c r="E175" s="6"/>
+      <c r="F175" s="6">
+        <v>277500</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>14</v>
+      </c>
+      <c r="B176" t="s">
+        <v>14</v>
+      </c>
+      <c r="C176" t="s">
+        <v>106</v>
+      </c>
+      <c r="D176" t="s">
+        <v>107</v>
+      </c>
+      <c r="E176" s="6"/>
+      <c r="F176" s="6">
+        <v>49950</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>108</v>
+      </c>
+      <c r="B177" t="s">
+        <v>109</v>
+      </c>
+      <c r="C177" t="s">
+        <v>90</v>
+      </c>
+      <c r="D177" t="s">
+        <v>91</v>
+      </c>
+      <c r="E177" s="6">
+        <v>608880</v>
+      </c>
+      <c r="F177" s="6"/>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>14</v>
+      </c>
+      <c r="B178" t="s">
+        <v>14</v>
+      </c>
+      <c r="C178" t="s">
+        <v>104</v>
+      </c>
+      <c r="D178" t="s">
+        <v>105</v>
+      </c>
+      <c r="E178" s="6"/>
+      <c r="F178" s="6">
+        <v>516000</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>14</v>
+      </c>
+      <c r="B179" t="s">
+        <v>14</v>
+      </c>
+      <c r="C179" t="s">
+        <v>106</v>
+      </c>
+      <c r="D179" t="s">
+        <v>107</v>
+      </c>
+      <c r="E179" s="6"/>
+      <c r="F179" s="6">
+        <v>92880</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>110</v>
+      </c>
+      <c r="B180" t="s">
+        <v>111</v>
+      </c>
+      <c r="C180" t="s">
+        <v>90</v>
+      </c>
+      <c r="D180" t="s">
+        <v>91</v>
+      </c>
+      <c r="E180" s="6">
+        <v>1220120</v>
+      </c>
+      <c r="F180" s="6"/>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>14</v>
+      </c>
+      <c r="B181" t="s">
+        <v>14</v>
+      </c>
+      <c r="C181" t="s">
+        <v>104</v>
+      </c>
+      <c r="D181" t="s">
+        <v>105</v>
+      </c>
+      <c r="E181" s="6"/>
+      <c r="F181" s="6">
+        <v>1034000</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>14</v>
+      </c>
+      <c r="B182" t="s">
+        <v>14</v>
+      </c>
+      <c r="C182" t="s">
+        <v>106</v>
+      </c>
+      <c r="D182" t="s">
+        <v>107</v>
+      </c>
+      <c r="E182" s="6"/>
+      <c r="F182" s="6">
+        <v>186120</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>112</v>
+      </c>
+      <c r="B183" t="s">
+        <v>113</v>
+      </c>
+      <c r="C183" t="s">
+        <v>90</v>
+      </c>
+      <c r="D183" t="s">
+        <v>91</v>
+      </c>
+      <c r="E183" s="6">
+        <v>365800</v>
+      </c>
+      <c r="F183" s="6"/>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>14</v>
+      </c>
+      <c r="B184" t="s">
+        <v>14</v>
+      </c>
+      <c r="C184" t="s">
+        <v>104</v>
+      </c>
+      <c r="D184" t="s">
+        <v>105</v>
+      </c>
+      <c r="E184" s="6"/>
+      <c r="F184" s="6">
+        <v>310000</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>14</v>
+      </c>
+      <c r="B185" t="s">
+        <v>14</v>
+      </c>
+      <c r="C185" t="s">
+        <v>106</v>
+      </c>
+      <c r="D185" t="s">
+        <v>107</v>
+      </c>
+      <c r="E185" s="6"/>
+      <c r="F185" s="6">
+        <v>55800</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>114</v>
+      </c>
+      <c r="B186" t="s">
+        <v>115</v>
+      </c>
+      <c r="C186" t="s">
+        <v>90</v>
+      </c>
+      <c r="D186" t="s">
+        <v>91</v>
+      </c>
+      <c r="E186" s="6">
+        <v>637200</v>
+      </c>
+      <c r="F186" s="6"/>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>14</v>
+      </c>
+      <c r="B187" t="s">
+        <v>14</v>
+      </c>
+      <c r="C187" t="s">
+        <v>104</v>
+      </c>
+      <c r="D187" t="s">
+        <v>105</v>
+      </c>
+      <c r="E187" s="6"/>
+      <c r="F187" s="6">
+        <v>540000</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>14</v>
+      </c>
+      <c r="B188" t="s">
+        <v>14</v>
+      </c>
+      <c r="C188" t="s">
+        <v>106</v>
+      </c>
+      <c r="D188" t="s">
+        <v>107</v>
+      </c>
+      <c r="E188" s="6"/>
+      <c r="F188" s="6">
+        <v>97200</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>116</v>
+      </c>
+      <c r="B189" t="s">
+        <v>117</v>
+      </c>
+      <c r="C189" t="s">
+        <v>90</v>
+      </c>
+      <c r="D189" t="s">
+        <v>91</v>
+      </c>
+      <c r="E189" s="6">
+        <v>545750</v>
+      </c>
+      <c r="F189" s="6"/>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>14</v>
+      </c>
+      <c r="B190" t="s">
+        <v>14</v>
+      </c>
+      <c r="C190" t="s">
+        <v>104</v>
+      </c>
+      <c r="D190" t="s">
+        <v>105</v>
+      </c>
+      <c r="E190" s="6"/>
+      <c r="F190" s="6">
+        <v>462500</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>14</v>
+      </c>
+      <c r="B191" t="s">
+        <v>14</v>
+      </c>
+      <c r="C191" t="s">
+        <v>106</v>
+      </c>
+      <c r="D191" t="s">
+        <v>107</v>
+      </c>
+      <c r="E191" s="6"/>
+      <c r="F191" s="6">
+        <v>83250</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>118</v>
+      </c>
+      <c r="B192" t="s">
+        <v>119</v>
+      </c>
+      <c r="C192" t="s">
+        <v>90</v>
+      </c>
+      <c r="D192" t="s">
+        <v>91</v>
+      </c>
+      <c r="E192" s="6">
+        <v>1062000</v>
+      </c>
+      <c r="F192" s="6"/>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>14</v>
+      </c>
+      <c r="B193" t="s">
+        <v>14</v>
+      </c>
+      <c r="C193" t="s">
+        <v>120</v>
+      </c>
+      <c r="D193" t="s">
+        <v>121</v>
+      </c>
+      <c r="E193" s="6"/>
+      <c r="F193" s="6">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>14</v>
+      </c>
+      <c r="B194" t="s">
+        <v>14</v>
+      </c>
+      <c r="C194" t="s">
+        <v>106</v>
+      </c>
+      <c r="D194" t="s">
+        <v>107</v>
+      </c>
+      <c r="E194" s="6"/>
+      <c r="F194" s="6">
+        <v>162000</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>122</v>
+      </c>
+      <c r="B195" t="s">
+        <v>123</v>
+      </c>
+      <c r="C195" t="s">
+        <v>90</v>
+      </c>
+      <c r="D195" t="s">
+        <v>91</v>
+      </c>
+      <c r="E195" s="6">
+        <v>442500</v>
+      </c>
+      <c r="F195" s="6"/>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>14</v>
+      </c>
+      <c r="B196" t="s">
+        <v>14</v>
+      </c>
+      <c r="C196" t="s">
+        <v>120</v>
+      </c>
+      <c r="D196" t="s">
+        <v>121</v>
+      </c>
+      <c r="E196" s="6"/>
+      <c r="F196" s="6">
+        <v>375000</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>14</v>
+      </c>
+      <c r="B197" t="s">
+        <v>14</v>
+      </c>
+      <c r="C197" t="s">
+        <v>106</v>
+      </c>
+      <c r="D197" t="s">
+        <v>107</v>
+      </c>
+      <c r="E197" s="6"/>
+      <c r="F197" s="6">
+        <v>67500</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>124</v>
+      </c>
+      <c r="B198" t="s">
+        <v>125</v>
+      </c>
+      <c r="C198" t="s">
+        <v>90</v>
+      </c>
+      <c r="D198" t="s">
+        <v>91</v>
+      </c>
+      <c r="E198" s="6">
+        <v>578200</v>
+      </c>
+      <c r="F198" s="6"/>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>14</v>
+      </c>
+      <c r="B199" t="s">
+        <v>14</v>
+      </c>
+      <c r="C199" t="s">
+        <v>104</v>
+      </c>
+      <c r="D199" t="s">
+        <v>105</v>
+      </c>
+      <c r="E199" s="6"/>
+      <c r="F199" s="6">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>14</v>
+      </c>
+      <c r="B200" t="s">
+        <v>14</v>
+      </c>
+      <c r="C200" t="s">
+        <v>106</v>
+      </c>
+      <c r="D200" t="s">
+        <v>107</v>
+      </c>
+      <c r="E200" s="6"/>
+      <c r="F200" s="6">
+        <v>88200</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>126</v>
+      </c>
+      <c r="B201" t="s">
+        <v>127</v>
+      </c>
+      <c r="C201" t="s">
+        <v>90</v>
+      </c>
+      <c r="D201" t="s">
+        <v>91</v>
+      </c>
+      <c r="E201" s="6">
+        <v>861400</v>
+      </c>
+      <c r="F201" s="6"/>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>14</v>
+      </c>
+      <c r="B202" t="s">
+        <v>14</v>
+      </c>
+      <c r="C202" t="s">
+        <v>120</v>
+      </c>
+      <c r="D202" t="s">
+        <v>121</v>
+      </c>
+      <c r="E202" s="6"/>
+      <c r="F202" s="6">
+        <v>730000</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>14</v>
+      </c>
+      <c r="B203" t="s">
+        <v>14</v>
+      </c>
+      <c r="C203" t="s">
+        <v>106</v>
+      </c>
+      <c r="D203" t="s">
+        <v>107</v>
+      </c>
+      <c r="E203" s="6"/>
+      <c r="F203" s="6">
+        <v>131400</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>128</v>
+      </c>
+      <c r="B204" t="s">
+        <v>129</v>
+      </c>
+      <c r="C204" t="s">
+        <v>90</v>
+      </c>
+      <c r="D204" t="s">
+        <v>91</v>
+      </c>
+      <c r="E204" s="6">
+        <v>925120</v>
+      </c>
+      <c r="F204" s="6"/>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>14</v>
+      </c>
+      <c r="B205" t="s">
+        <v>14</v>
+      </c>
+      <c r="C205" t="s">
+        <v>104</v>
+      </c>
+      <c r="D205" t="s">
+        <v>105</v>
+      </c>
+      <c r="E205" s="6"/>
+      <c r="F205" s="6">
+        <v>784000</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>14</v>
+      </c>
+      <c r="B206" t="s">
+        <v>14</v>
+      </c>
+      <c r="C206" t="s">
+        <v>106</v>
+      </c>
+      <c r="D206" t="s">
+        <v>107</v>
+      </c>
+      <c r="E206" s="6"/>
+      <c r="F206" s="6">
         <v>141120</v>
       </c>
     </row>
-    <row r="79" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B79" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D79" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E79" s="9">
+    <row r="207" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A207" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B207" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C207" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D207" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="E207" s="9">
         <v>7574420</v>
       </c>
-      <c r="F79" s="9">
+      <c r="F207" s="9">
         <v>7574420</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="10" t="s">
-        <v>84</v>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A209" s="10" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -2044,8 +4489,8 @@
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A158:F158"/>
+    <mergeCell ref="A172:F172"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
